--- a/Reports/sanityReport.xlsx
+++ b/Reports/sanityReport.xlsx
@@ -29,40 +29,40 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>9769 ms</t>
+    <t>6867 ms</t>
   </si>
   <si>
-    <t>createLead_WithOnlyRequiredFields</t>
+    <t>createLead_WithAllDetails</t>
   </si>
   <si>
-    <t>26893 ms</t>
+    <t>54308 ms</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t>30750 ms</t>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>44794 ms</t>
   </si>
   <si>
     <t>addTask</t>
   </si>
   <si>
-    <t>33405 ms</t>
+    <t>35132 ms</t>
   </si>
   <si>
     <t>addMeeting</t>
   </si>
   <si>
-    <t>15769 ms</t>
+    <t>1093 ms</t>
   </si>
   <si>
     <t>email</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>1148 ms</t>
+    <t>1162 ms</t>
   </si>
 </sst>
 </file>
@@ -148,40 +148,40 @@
         <v>8</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>16</v>
